--- a/files/九龙-启德-维港．湾畔第2B期.xlsx
+++ b/files/九龙-启德-维港．湾畔第2B期.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -25992,4770 +25855,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:K32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>维港．湾畔第2B期 - 5A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>270 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>270 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K18" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K21" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K22" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K23" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K24" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K26" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K27" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K28" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K29" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K30" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K31" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K32" s="16" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>维港．湾畔第2B期 - 5B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>239 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>35 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>203 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1839呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 752呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 448呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-$2,576万
-$38,622/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-$2,551万
-$38,240/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$3,211万
-$43,163/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-$2,463万
-$36,930/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$2,663万
-$35,792/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-$2,236万
-$33,522/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$2,575万
-$34,614/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-$2,225万
-$33,357/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$3,069万
-$41,246/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-$2,342万
-$35,105/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$3,094万
-$41,586/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$3,080万
-$41,403/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$2,524万
-$33,929/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-$2,181万
-$32,697/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$2,512万
-$33,761/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-$2,295万
-$34,411/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$2,985万
-$40,126/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-$2,220万
-$33,279/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$2,462万
-$33,089/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-$2,127万
-$31,885/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$2,450万
-$32,925/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-$2,116万
-$31,726/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$2,437万
-$32,759/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-$2,106万
-$31,567/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$2,425万
-$32,595/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-$2,135万
-$32,013/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$2,413万
-$32,433/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-$2,245万
-$33,657/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$2,401万
-$32,270/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-$2,212万
-$33,156/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$2,388万
-$32,091/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-$2,195万
-$32,909/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$2,364万
-$31,770/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>A | 744呎 (3房)
-$2,306万
-$30,996/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>B | 667呎 (3房)
-$1,951万
-$29,244/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>D | 662呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>E | 314呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>F | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>G | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>H | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>J | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-启德-维港．湾畔第2B期.xlsx
+++ b/files/九龙-启德-维港．湾畔第2B期.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +143,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +224,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -25855,4 +26035,4770 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K26" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K28" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K29" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J30" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K30" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K31" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1839呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 752呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 448呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+$2576万
+$38,622/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+$2551万
+$38,240/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$3211万
+$43,163/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+$2463万
+$36,930/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$2663万
+$35,792/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+$2236万
+$33,522/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$2575万
+$34,614/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+$2225万
+$33,357/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$3069万
+$41,246/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+$2342万
+$35,105/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$3094万
+$41,586/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$3080万
+$41,403/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$2524万
+$33,929/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+$2181万
+$32,697/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$2512万
+$33,761/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+$2295万
+$34,411/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$2985万
+$40,126/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+$2220万
+$33,279/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$2462万
+$33,089/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+$2127万
+$31,885/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$2450万
+$32,925/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+$2116万
+$31,726/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$2437万
+$32,759/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+$2106万
+$31,567/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$2425万
+$32,595/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+$2135万
+$32,013/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$2413万
+$32,433/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+$2245万
+$33,657/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$2401万
+$32,270/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+$2212万
+$33,156/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$2388万
+$32,091/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+$2195万
+$32,909/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$2364万
+$31,770/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J30" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 744呎 (3房)
+$2306万
+$30,996/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 667呎 (3房)
+$1951万
+$29,244/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 662呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 314呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>F | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>G | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>H | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
+        <is>
+          <t>J | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-维港．湾畔第2B期.xlsx
+++ b/files/九龙-启德-维港．湾畔第2B期.xlsx
@@ -654,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -17991,7 +17991,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -29312,7 +29312,7 @@
           <t>B | 667呎 (3房)
 $2463万
 $36,930/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">

--- a/files/九龙-启德-维港．湾畔第2B期.xlsx
+++ b/files/九龙-启德-维港．湾畔第2B期.xlsx
@@ -21773,7 +21773,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -34883,7 +34883,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H492" s="5" t="n">
@@ -39121,7 +39121,7 @@
           <t>B | 667呎 (3房)
 $2576万
 $38,622/呎
-(26年-06月-23日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -40780,7 +40780,7 @@
           <t>B | 667呎 (3房)
 $2195万
 $32,909/呎
-(26年-06月-19日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">

--- a/files/九龙-启德-维港．湾畔第2B期.xlsx
+++ b/files/九龙-启德-维港．湾畔第2B期.xlsx
@@ -39121,7 +39121,7 @@
           <t>B | 667呎 (3房)
 $2576万
 $38,622/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -39200,7 +39200,7 @@
           <t>B | 667呎 (3房)
 $2551万
 $38,240/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -39508,7 +39508,7 @@
           <t>A | 744呎 (3房)
 $3211万
 $43,163/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -39516,7 +39516,7 @@
           <t>B | 667呎 (3房)
 $2463万
 $36,930/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -39587,7 +39587,7 @@
           <t>A | 744呎 (3房)
 $2663万
 $35,792/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -39595,7 +39595,7 @@
           <t>B | 667呎 (3房)
 $2236万
 $33,522/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -39666,7 +39666,7 @@
           <t>A | 744呎 (3房)
 $2575万
 $34,614/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -39674,7 +39674,7 @@
           <t>B | 667呎 (3房)
 $2225万
 $33,357/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -39745,7 +39745,7 @@
           <t>A | 744呎 (3房)
 $3069万
 $41,246/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -39753,7 +39753,7 @@
           <t>B | 667呎 (3房)
 $2342万
 $35,105/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -39824,7 +39824,7 @@
           <t>A | 744呎 (3房)
 $3094万
 $41,586/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -39903,7 +39903,7 @@
           <t>A | 744呎 (3房)
 $3080万
 $41,403/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -39982,7 +39982,7 @@
           <t>A | 744呎 (3房)
 $2524万
 $33,929/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -39990,7 +39990,7 @@
           <t>B | 667呎 (3房)
 $2181万
 $32,697/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -40061,7 +40061,7 @@
           <t>A | 744呎 (3房)
 $2512万
 $33,761/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -40069,7 +40069,7 @@
           <t>B | 667呎 (3房)
 $2295万
 $34,411/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -40219,7 +40219,7 @@
           <t>A | 744呎 (3房)
 $2985万
 $40,126/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -40227,7 +40227,7 @@
           <t>B | 667呎 (3房)
 $2220万
 $33,279/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -40298,7 +40298,7 @@
           <t>A | 744呎 (3房)
 $2462万
 $33,089/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -40306,7 +40306,7 @@
           <t>B | 667呎 (3房)
 $2127万
 $31,885/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -40377,7 +40377,7 @@
           <t>A | 744呎 (3房)
 $2450万
 $32,925/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -40385,7 +40385,7 @@
           <t>B | 667呎 (3房)
 $2116万
 $31,726/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -40456,7 +40456,7 @@
           <t>A | 744呎 (3房)
 $2437万
 $32,759/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -40464,7 +40464,7 @@
           <t>B | 667呎 (3房)
 $2106万
 $31,567/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -40535,7 +40535,7 @@
           <t>A | 744呎 (3房)
 $2425万
 $32,595/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -40543,7 +40543,7 @@
           <t>B | 667呎 (3房)
 $2135万
 $32,013/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -40614,7 +40614,7 @@
           <t>A | 744呎 (3房)
 $2413万
 $32,433/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -40622,7 +40622,7 @@
           <t>B | 667呎 (3房)
 $2245万
 $33,657/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -40693,7 +40693,7 @@
           <t>A | 744呎 (3房)
 $2401万
 $32,270/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -40701,7 +40701,7 @@
           <t>B | 667呎 (3房)
 $2212万
 $33,156/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -40772,7 +40772,7 @@
           <t>A | 744呎 (3房)
 $2388万
 $32,091/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -40780,7 +40780,7 @@
           <t>B | 667呎 (3房)
 $2195万
 $32,909/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -40851,7 +40851,7 @@
           <t>A | 744呎 (3房)
 $2364万
 $31,770/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -40930,7 +40930,7 @@
           <t>A | 744呎 (3房)
 $2306万
 $30,996/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -40938,7 +40938,7 @@
           <t>B | 667呎 (3房)
 $1951万
 $29,244/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">

--- a/files/九龙-启德-维港．湾畔第2B期.xlsx
+++ b/files/九龙-启德-维港．湾畔第2B期.xlsx
@@ -39121,7 +39121,7 @@
           <t>B | 667呎 (3房)
 $2576万
 $38,622/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -39200,7 +39200,7 @@
           <t>B | 667呎 (3房)
 $2551万
 $38,240/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -39508,7 +39508,7 @@
           <t>A | 744呎 (3房)
 $3211万
 $43,163/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -39516,7 +39516,7 @@
           <t>B | 667呎 (3房)
 $2463万
 $36,930/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -39587,7 +39587,7 @@
           <t>A | 744呎 (3房)
 $2663万
 $35,792/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -39595,7 +39595,7 @@
           <t>B | 667呎 (3房)
 $2236万
 $33,522/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -39666,7 +39666,7 @@
           <t>A | 744呎 (3房)
 $2575万
 $34,614/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -39674,7 +39674,7 @@
           <t>B | 667呎 (3房)
 $2225万
 $33,357/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -39745,7 +39745,7 @@
           <t>A | 744呎 (3房)
 $3069万
 $41,246/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -39753,7 +39753,7 @@
           <t>B | 667呎 (3房)
 $2342万
 $35,105/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -39824,7 +39824,7 @@
           <t>A | 744呎 (3房)
 $3094万
 $41,586/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -39903,7 +39903,7 @@
           <t>A | 744呎 (3房)
 $3080万
 $41,403/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -39982,7 +39982,7 @@
           <t>A | 744呎 (3房)
 $2524万
 $33,929/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -39990,7 +39990,7 @@
           <t>B | 667呎 (3房)
 $2181万
 $32,697/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -40061,7 +40061,7 @@
           <t>A | 744呎 (3房)
 $2512万
 $33,761/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -40069,7 +40069,7 @@
           <t>B | 667呎 (3房)
 $2295万
 $34,411/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -40219,7 +40219,7 @@
           <t>A | 744呎 (3房)
 $2985万
 $40,126/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -40227,7 +40227,7 @@
           <t>B | 667呎 (3房)
 $2220万
 $33,279/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -40298,7 +40298,7 @@
           <t>A | 744呎 (3房)
 $2462万
 $33,089/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -40306,7 +40306,7 @@
           <t>B | 667呎 (3房)
 $2127万
 $31,885/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -40377,7 +40377,7 @@
           <t>A | 744呎 (3房)
 $2450万
 $32,925/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -40385,7 +40385,7 @@
           <t>B | 667呎 (3房)
 $2116万
 $31,726/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -40456,7 +40456,7 @@
           <t>A | 744呎 (3房)
 $2437万
 $32,759/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -40464,7 +40464,7 @@
           <t>B | 667呎 (3房)
 $2106万
 $31,567/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -40535,7 +40535,7 @@
           <t>A | 744呎 (3房)
 $2425万
 $32,595/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -40543,7 +40543,7 @@
           <t>B | 667呎 (3房)
 $2135万
 $32,013/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -40614,7 +40614,7 @@
           <t>A | 744呎 (3房)
 $2413万
 $32,433/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -40622,7 +40622,7 @@
           <t>B | 667呎 (3房)
 $2245万
 $33,657/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -40693,7 +40693,7 @@
           <t>A | 744呎 (3房)
 $2401万
 $32,270/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -40701,7 +40701,7 @@
           <t>B | 667呎 (3房)
 $2212万
 $33,156/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -40772,7 +40772,7 @@
           <t>A | 744呎 (3房)
 $2388万
 $32,091/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -40780,7 +40780,7 @@
           <t>B | 667呎 (3房)
 $2195万
 $32,909/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -40851,7 +40851,7 @@
           <t>A | 744呎 (3房)
 $2364万
 $31,770/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -40930,7 +40930,7 @@
           <t>A | 744呎 (3房)
 $2306万
 $30,996/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -40938,7 +40938,7 @@
           <t>B | 667呎 (3房)
 $1951万
 $29,244/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">

--- a/files/九龙-启德-维港．湾畔第2B期.xlsx
+++ b/files/九龙-启德-维港．湾畔第2B期.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,12 +125,6 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -208,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -274,9 +268,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -35500,23 +35491,19 @@
       </c>
       <c r="F501" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H501" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I501" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="H501" s="5" t="n">
+        <v>21512000</v>
+      </c>
+      <c r="I501" s="5" t="n">
+        <v>32252</v>
       </c>
       <c r="J501" s="3" t="inlineStr">
         <is>
@@ -35525,12 +35512,12 @@
       </c>
       <c r="K501" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L501" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M501" s="3" t="inlineStr">
@@ -35540,7 +35527,7 @@
       </c>
       <c r="N501" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38817,7 +38804,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -38827,7 +38814,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40854,12 +40841,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
-招标单位
--
-(在售)</t>
+$2151万
+$32,252/呎
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
